--- a/tc/공지사항_TC_2026-10_v3.xlsx
+++ b/tc/공지사항_TC_2026-10_v3.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="366">
   <si>
     <t>No.</t>
   </si>
@@ -218,7 +218,12 @@
   </si>
   <si>
     <t xml:space="preserve">1. 공지 제목 노출
-2. "등록:" 등 접두 라벨 없이 날짜(범위)만 노출</t>
+2. "등록:" 등 접두 라벨 없이 날짜(범위)만 노출
+3. 시작일(등록일)은 항상 날짜만(시각 없음)
+4. 만료일 있으면 "등록일 ~ 만료일 23:59" 범위(한국어=라벨없음 / 그 외 언어=23:59 KST)</t>
+  </si>
+  <si>
+    <t>2026-10-01: 만료일 "23:59" 고정 표기(표시 전용 문구, 저장값 아님). 공지 시작일은 시각 개념 없음.</t>
   </si>
   <si>
     <t>정렬</t>
@@ -606,11 +611,12 @@
     <t>1. front 목록·상세 날짜 시간대 확인</t>
   </si>
   <si>
-    <t xml:space="preserve">1. KST 기준으로 노출
-2. 한국 외 국가 현지시간 환산은 미구현 — KST 원본 + "KST" 라벨만 임시 노출</t>
-  </si>
-  <si>
-    <t>D7 정상/보류(ISSUE-079). front에 "환산됨" 표기가 보이면 오히려 이상. 저장=KST(2026-08-19 정정).</t>
+    <t xml:space="preserve">1. 저장=KST. 시작일(등록일)은 언어 무관 날짜만(시각 없음)
+2. 만료일은 "23:59" 고정 표기 — 한국어=라벨없음, 그 외 언어=23:59 KST
+3. 국가별 현지시간 환산은 미구현(보류)</t>
+  </si>
+  <si>
+    <t>2026-10-01 재확정. 공지 시각값 없음 — "23:59"는 표시 전용 고정 문구(만료 당일 23:59까지 노출→익일 00:00 미노출). 환산됨 표기 보이면 이상(ISSUE-079).</t>
   </si>
   <si>
     <t>연계·상태라벨</t>
@@ -2084,7 +2090,7 @@
         <v>23</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -2095,19 +2101,19 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>22</v>
@@ -2129,7 +2135,7 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>16</v>
@@ -2141,10 +2147,10 @@
         <v>57</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>22</v>
@@ -2167,19 +2173,19 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>22</v>
@@ -2202,19 +2208,19 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>22</v>
@@ -2237,19 +2243,19 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>22</v>
@@ -2272,19 +2278,19 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>22</v>
@@ -2296,7 +2302,7 @@
         <v>23</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -2307,19 +2313,19 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>22</v>
@@ -2341,10 +2347,10 @@
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>26</v>
@@ -2353,10 +2359,10 @@
         <v>57</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>22</v>
@@ -2379,19 +2385,19 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>22</v>
@@ -2413,22 +2419,22 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>22</v>
@@ -2450,22 +2456,22 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>22</v>
@@ -2477,7 +2483,7 @@
         <v>23</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -2487,25 +2493,25 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>23</v>
@@ -2514,7 +2520,7 @@
         <v>23</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -2525,22 +2531,22 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>23</v>
@@ -2549,7 +2555,7 @@
         <v>23</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -2559,25 +2565,25 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>23</v>
@@ -2586,7 +2592,7 @@
         <v>23</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -2597,22 +2603,22 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>23</v>
@@ -2621,7 +2627,7 @@
         <v>23</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -2632,22 +2638,22 @@
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>23</v>
@@ -2656,7 +2662,7 @@
         <v>23</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -2666,25 +2672,25 @@
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>23</v>
@@ -2693,7 +2699,7 @@
         <v>23</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -2704,22 +2710,22 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>23</v>
@@ -2728,7 +2734,7 @@
         <v>23</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -2739,22 +2745,22 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>23</v>
@@ -2763,7 +2769,7 @@
         <v>23</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -2773,25 +2779,25 @@
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>23</v>
@@ -2800,7 +2806,7 @@
         <v>23</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -2811,22 +2817,22 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>23</v>
@@ -2835,7 +2841,7 @@
         <v>23</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -2846,22 +2852,22 @@
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>23</v>
@@ -2870,7 +2876,7 @@
         <v>23</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -2880,25 +2886,25 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>23</v>
@@ -2907,7 +2913,7 @@
         <v>23</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -2918,22 +2924,22 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>23</v>
@@ -2942,7 +2948,7 @@
         <v>23</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -2952,25 +2958,25 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>23</v>
@@ -2979,7 +2985,7 @@
         <v>23</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -2989,25 +2995,25 @@
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>23</v>
@@ -3016,7 +3022,7 @@
         <v>23</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -3026,25 +3032,25 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>23</v>
@@ -3053,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -3063,25 +3069,25 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>23</v>
@@ -3090,7 +3096,7 @@
         <v>23</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -3101,22 +3107,22 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>23</v>
@@ -3125,7 +3131,7 @@
         <v>23</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -3136,22 +3142,22 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>23</v>
@@ -3160,7 +3166,7 @@
         <v>23</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -3171,22 +3177,22 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>23</v>
@@ -3195,7 +3201,7 @@
         <v>23</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -3206,22 +3212,22 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>23</v>
@@ -3230,7 +3236,7 @@
         <v>23</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -3241,22 +3247,22 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>23</v>
@@ -3265,7 +3271,7 @@
         <v>23</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -3275,25 +3281,25 @@
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>23</v>
@@ -3302,7 +3308,7 @@
         <v>23</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -3313,22 +3319,22 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>23</v>
@@ -3337,7 +3343,7 @@
         <v>23</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -3348,22 +3354,22 @@
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>23</v>
@@ -3372,7 +3378,7 @@
         <v>23</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -3383,22 +3389,22 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>23</v>
@@ -3407,7 +3413,7 @@
         <v>23</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -3417,25 +3423,25 @@
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>23</v>
@@ -3444,7 +3450,7 @@
         <v>23</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -3455,22 +3461,22 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>23</v>
@@ -3479,7 +3485,7 @@
         <v>23</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -3490,22 +3496,22 @@
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>23</v>
@@ -3514,7 +3520,7 @@
         <v>23</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -3525,22 +3531,22 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>23</v>
@@ -3549,7 +3555,7 @@
         <v>23</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -3559,25 +3565,25 @@
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>23</v>
@@ -3586,7 +3592,7 @@
         <v>23</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -3597,22 +3603,22 @@
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>23</v>
@@ -3621,7 +3627,7 @@
         <v>23</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -3632,22 +3638,22 @@
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>23</v>
@@ -3656,7 +3662,7 @@
         <v>23</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -3667,22 +3673,22 @@
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>23</v>
@@ -3691,7 +3697,7 @@
         <v>23</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -3701,25 +3707,25 @@
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>23</v>
@@ -3728,7 +3734,7 @@
         <v>23</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -3739,22 +3745,22 @@
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>23</v>
@@ -3763,7 +3769,7 @@
         <v>23</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -3774,22 +3780,22 @@
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>23</v>
@@ -3798,7 +3804,7 @@
         <v>23</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -3808,25 +3814,25 @@
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>23</v>
@@ -3835,7 +3841,7 @@
         <v>23</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -3846,22 +3852,22 @@
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>23</v>
@@ -3870,7 +3876,7 @@
         <v>23</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -3881,22 +3887,22 @@
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>23</v>
@@ -3905,7 +3911,7 @@
         <v>23</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -3915,25 +3921,25 @@
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>23</v>
@@ -3942,7 +3948,7 @@
         <v>23</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -3953,22 +3959,22 @@
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>23</v>
@@ -3977,7 +3983,7 @@
         <v>23</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -3987,25 +3993,25 @@
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>23</v>
@@ -4014,7 +4020,7 @@
         <v>23</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -4025,22 +4031,22 @@
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>23</v>
@@ -4049,7 +4055,7 @@
         <v>23</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -4060,22 +4066,22 @@
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>23</v>
@@ -4084,7 +4090,7 @@
         <v>23</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -4095,22 +4101,22 @@
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>23</v>
@@ -4119,7 +4125,7 @@
         <v>23</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -4129,25 +4135,25 @@
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>23</v>
@@ -4156,7 +4162,7 @@
         <v>23</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -4167,22 +4173,22 @@
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>23</v>
@@ -4191,7 +4197,7 @@
         <v>23</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -4202,22 +4208,22 @@
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>23</v>
@@ -4226,7 +4232,7 @@
         <v>23</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -4236,25 +4242,25 @@
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>23</v>
@@ -4263,7 +4269,7 @@
         <v>23</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
